--- a/contabilidad_meli.xlsx
+++ b/contabilidad_meli.xlsx
@@ -200,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Resumen Diario'!$A$2</f>
+              <f>'Resumen Diario'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Resumen Diario'!$D$2</f>
+              <f>'Resumen Diario'!$D$2:$D$3</f>
             </numRef>
           </val>
         </ser>
@@ -232,12 +232,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Resumen Diario'!$A$2</f>
+              <f>'Resumen Diario'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Resumen Diario'!$K$2</f>
+              <f>'Resumen Diario'!$K$2:$K$3</f>
             </numRef>
           </val>
         </ser>
@@ -318,7 +318,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>NET por cuenta — 2026-04-24</a:t>
+              <a:t>NET por cuenta — 2026-04-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -378,7 +378,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Top 10 productos — 2026-04-24</a:t>
+              <a:t>Top 10 productos — 2026-04-25</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -403,12 +403,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Gráficas'!$A$41:$A$43</f>
+              <f>'Gráficas'!$A$41:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Gráficas'!$B$41:$B$43</f>
+              <f>'Gráficas'!$B$41:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -838,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -960,6 +960,49 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>30826</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4117.02</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3327.5</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>4251.862068965516</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="3">
+        <f>D3-E3-F3</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
+        <f>J3-G3</f>
+        <v/>
+      </c>
+      <c r="L3" s="4">
+        <f>IFERROR(K3/D3,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -971,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1142,6 +1185,98 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HFCBHDGAE33468</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7787</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1129.18</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>1074.068965517241</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>599</v>
+      </c>
+      <c r="K4" s="3">
+        <f>F4-G4-H4</f>
+        <v/>
+      </c>
+      <c r="L4" s="4">
+        <f>IFERROR(K4/F4,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CX20260420180750</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>23039</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2987.84</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>2309</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3177.793103448275</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>603</v>
+      </c>
+      <c r="K5" s="3">
+        <f>F5-G5-H5</f>
+        <v/>
+      </c>
+      <c r="L5" s="4">
+        <f>IFERROR(K5/F5,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1153,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1259,6 +1394,328 @@
         <v>299</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 Nueva Original Color</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7787</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Parlante Bluetooth Jbl Flip 7 Resistente Al Agua Y Polvo Ip6</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6495</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Cel</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Roj</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Armaf Delight Island Bliss Edp 100 Ml Para Mujer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Jbl Go 4 Bluetooth, Camuflaje. Color Camufla</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Angel Nova Fruitté Edp Para Mujer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Parlante Bluetooth Jbl Go 4 Portátil Rosa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Azu</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Grip Bluetooth Portátil Ip68 14 H Batería Negro</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Armaf Odyssey Mega Man Edición Limitada Edp 100 Ml</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Armaf Club De Nuit Maleka Edp Mujer 105ml</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Perfume Lattafa His Confession 100ml Edp Para Caballero</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Perfume Armaf Odyssey Spectra Hombre 100ml Eau De Parfum</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1270,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1343,6 +1800,66 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2000016142393670</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 Nueva Original Color</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>599</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2000016143278512</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Jbl Go 4 Bluetooth, Camuflaje. Color Camufla</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>603</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>cancelled</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1354,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A22:B43"/>
+  <dimension ref="A22:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1380,18 +1897,18 @@
         </is>
       </c>
       <c r="B23">
-        <f>F2-G2-H2</f>
+        <f>F4-G4-H4</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>CLARIBEL</t>
         </is>
       </c>
       <c r="B24">
-        <f>F3-G3-H3</f>
+        <f>F5-G5-H5</f>
         <v/>
       </c>
     </row>
@@ -1414,27 +1931,97 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15873</v>
+        <v>7787</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Sumergible Ip67 Bluetooth Bass 7h Seminueva</t>
+          <t>Parlante Bluetooth Jbl Flip 7 Resistente Al Agua Y Polvo Ip6</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>598</v>
+        <v>6495</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 - Usada</t>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Cel</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>299</v>
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Roj</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Armaf Delight Island Bliss Edp 100 Ml Para Mujer</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Bocina Portátil Jbl Go 4 Bluetooth, Camuflaje. Color Camufla</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Angel Nova Fruitté Edp Para Mujer</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Parlante Bluetooth Jbl Go 4 Portátil Rosa</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Azu</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Bocina Jbl Grip Bluetooth Portátil Ip68 14 H Batería Negro</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>966</v>
       </c>
     </row>
   </sheetData>

--- a/contabilidad_meli.xlsx
+++ b/contabilidad_meli.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Top Productos" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Devoluciones" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Gráficas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Mensual 2026-04" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +39,24 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -79,6 +98,19 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,7 +189,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -478,6 +509,148 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Bocinas por modelo — 2026-04</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Mensual 2026-04'!D25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Mensual 2026-04'!$A$26:$A$30</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mensual 2026-04'!$D$26:$D$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Devoluciones por motivo — 2026-04</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Mensual 2026-04'!C50</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Mensual 2026-04'!$A$51</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Mensual 2026-04'!$C$51</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -541,6 +714,55 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2028,4 +2250,839 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>📊 CIERRE MENSUAL — 2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Órdenes Totales</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Unidades Vendidas</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Bruto</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>99491</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Comisión MELI</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>14032.72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Envío Seller</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>17982.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>IVA Remite</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>13722.89655172413</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Devoluciones #</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Devoluciones $</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>162970.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>NET (sin IVA)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>67475.98</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>NET (post IVA)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>53753.08344827587</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Margen %</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.6782118985636891</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>📊 POR CUENTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Órdenes</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Bruto</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Comisión</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>Envío</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>Devol $</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>NET</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>Margen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>JUAN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HFCBHDGAE33468</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>71673</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>10039.88</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>14560.5</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>9885.931034482754</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>162367.5</v>
+      </c>
+      <c r="J18" s="3">
+        <f>E18-F18-G18</f>
+        <v/>
+      </c>
+      <c r="K18" s="4">
+        <f>IFERROR(J18/E18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CX20260420180750</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>23039</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2987.84</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>2309</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>3177.793103448275</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>603</v>
+      </c>
+      <c r="J19" s="3">
+        <f>E19-F19-G19</f>
+        <v/>
+      </c>
+      <c r="K19" s="4">
+        <f>IFERROR(J19/E19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ASVA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ASVAELECTRONICS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>3882</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>915.3000000000003</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>412.8000000000001</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>535.4482758620688</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <f>E20-F20-G20</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>IFERROR(J20/E20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>RAYMUNDO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RG20260415180857</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>897</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>89.69999999999999</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>123.7241379310344</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <f>E21-F21-G21</f>
+        <v/>
+      </c>
+      <c r="K21" s="4">
+        <f>IFERROR(J21/E21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>🎵 BOCINAS POR MODELO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>% Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JBL Go 4</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bocina</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>65581</v>
+      </c>
+      <c r="E26" s="4">
+        <f>IFERROR(D26/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>JBL Flip 7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bocina</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>11485</v>
+      </c>
+      <c r="E27" s="4">
+        <f>IFERROR(D27/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JBL Charge 6</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bocina</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>7935</v>
+      </c>
+      <c r="E28" s="4">
+        <f>IFERROR(D28/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JBL Grip</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bocina</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>2772</v>
+      </c>
+      <c r="E29" s="4">
+        <f>IFERROR(D29/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JBL Clip 5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bocina</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1894</v>
+      </c>
+      <c r="E30" s="4">
+        <f>IFERROR(D30/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>🌸 PERFUMES POR MARCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>% Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Armaf Delight</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2109</v>
+      </c>
+      <c r="E35" s="4">
+        <f>IFERROR(D35/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Mugler/Angel</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1743</v>
+      </c>
+      <c r="E36" s="4">
+        <f>IFERROR(D36/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Armaf Odyssey</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1196</v>
+      </c>
+      <c r="E37" s="4">
+        <f>IFERROR(D37/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Armaf Club De Nuit</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>499</v>
+      </c>
+      <c r="E38" s="4">
+        <f>IFERROR(D38/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Lattafa</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Perfume</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="E39" s="4">
+        <f>IFERROR(D39/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>🎧 OTROS PRODUCTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Unidades</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>% Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Conjunto Deportivo Animal Prin</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3384</v>
+      </c>
+      <c r="E44" s="4">
+        <f>IFERROR(D44/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Conjunto Deportivo Seamless Pr</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="E45" s="4">
+        <f>IFERROR(D45/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Conjunto Seamless Negro Moldea</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="E46" s="4">
+        <f>IFERROR(D46/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>↩️ DEVOLUCIONES POR MOTIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Motivo</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t># Devoluciones</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>Monto Reembolsado</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>% del Total Bruto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cancelled (sin claim)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>162970.5</v>
+      </c>
+      <c r="D51" s="4">
+        <f>IFERROR(C51/99491,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>162970.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/contabilidad_meli.xlsx
+++ b/contabilidad_meli.xlsx
@@ -591,66 +591,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Devoluciones por motivo — 2026-04</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Mensual 2026-04'!C50</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Mensual 2026-04'!$A$51</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Mensual 2026-04'!$C$51</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showPercent val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -741,28 +681,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>12</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5040000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2258,7 +2176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2300,7 +2218,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
@@ -2310,7 +2228,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -2320,7 +2238,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>99491</v>
+        <v>101056</v>
       </c>
     </row>
     <row r="7">
@@ -2330,7 +2248,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>14032.72</v>
+        <v>14232.69</v>
       </c>
     </row>
     <row r="8">
@@ -2340,7 +2258,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>17982.3</v>
+        <v>18117.8</v>
       </c>
     </row>
     <row r="9">
@@ -2350,7 +2268,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>13722.89655172413</v>
+        <v>13938.75862068965</v>
       </c>
     </row>
     <row r="10">
@@ -2360,7 +2278,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2370,7 +2288,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>162970.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2380,7 +2298,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>67475.98</v>
+        <v>68705.50999999999</v>
       </c>
     </row>
     <row r="13">
@@ -2390,7 +2308,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>53753.08344827587</v>
+        <v>54766.75137931035</v>
       </c>
     </row>
     <row r="14">
@@ -2400,7 +2318,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.6782118985636891</v>
+        <v>0.6798756135212159</v>
       </c>
     </row>
     <row r="16">
@@ -2497,7 +2415,7 @@
         <v>9885.931034482754</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>162367.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3">
         <f>E18-F18-G18</f>
@@ -2520,25 +2438,25 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>23039</v>
+        <v>24604</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2987.84</v>
+        <v>3187.81</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2309</v>
+        <v>2444.5</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3177.793103448275</v>
+        <v>3393.65517241379</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3">
         <f>E19-F19-G19</f>
@@ -2677,13 +2595,13 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>65581</v>
+        <v>66180</v>
       </c>
       <c r="E26" s="4">
-        <f>IFERROR(D26/99491,0)</f>
+        <f>IFERROR(D26/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2705,7 +2623,7 @@
         <v>11485</v>
       </c>
       <c r="E27" s="4">
-        <f>IFERROR(D27/99491,0)</f>
+        <f>IFERROR(D27/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2727,7 +2645,7 @@
         <v>7935</v>
       </c>
       <c r="E28" s="4">
-        <f>IFERROR(D28/99491,0)</f>
+        <f>IFERROR(D28/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2743,13 +2661,13 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2772</v>
+        <v>3738</v>
       </c>
       <c r="E29" s="4">
-        <f>IFERROR(D29/99491,0)</f>
+        <f>IFERROR(D29/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2771,7 +2689,7 @@
         <v>1894</v>
       </c>
       <c r="E30" s="4">
-        <f>IFERROR(D30/99491,0)</f>
+        <f>IFERROR(D30/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2827,7 +2745,7 @@
         <v>2109</v>
       </c>
       <c r="E35" s="4">
-        <f>IFERROR(D35/99491,0)</f>
+        <f>IFERROR(D35/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2849,7 +2767,7 @@
         <v>1743</v>
       </c>
       <c r="E36" s="4">
-        <f>IFERROR(D36/99491,0)</f>
+        <f>IFERROR(D36/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2871,7 +2789,7 @@
         <v>1196</v>
       </c>
       <c r="E37" s="4">
-        <f>IFERROR(D37/99491,0)</f>
+        <f>IFERROR(D37/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2893,7 +2811,7 @@
         <v>499</v>
       </c>
       <c r="E38" s="4">
-        <f>IFERROR(D38/99491,0)</f>
+        <f>IFERROR(D38/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2915,7 +2833,7 @@
         <v>395</v>
       </c>
       <c r="E39" s="4">
-        <f>IFERROR(D39/99491,0)</f>
+        <f>IFERROR(D39/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2971,7 +2889,7 @@
         <v>3384</v>
       </c>
       <c r="E44" s="4">
-        <f>IFERROR(D44/99491,0)</f>
+        <f>IFERROR(D44/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -2993,7 +2911,7 @@
         <v>299</v>
       </c>
       <c r="E45" s="4">
-        <f>IFERROR(D45/99491,0)</f>
+        <f>IFERROR(D45/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -3015,7 +2933,7 @@
         <v>199</v>
       </c>
       <c r="E46" s="4">
-        <f>IFERROR(D46/99491,0)</f>
+        <f>IFERROR(D46/101056,0)</f>
         <v/>
       </c>
     </row>
@@ -3049,33 +2967,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cancelled (sin claim)</t>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>162970.5</v>
-      </c>
-      <c r="D51" s="4">
-        <f>IFERROR(C51/99491,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>236</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>162970.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/contabilidad_meli.xlsx
+++ b/contabilidad_meli.xlsx
@@ -189,6 +189,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1107,28 +1108,28 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>30826</v>
+        <v>83292</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4117.02</v>
+        <v>10568.16999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3327.5</v>
+        <v>8204.199999999995</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>4251.862068965516</v>
+        <v>11488.55172413792</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1202</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3">
         <f>D3-E3-F3</f>
@@ -1342,25 +1343,25 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7787</v>
+        <v>11910</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1129.18</v>
+        <v>1703.239999999999</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1018.5</v>
+        <v>1517.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1074.068965517241</v>
+        <v>1642.758620689654</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>599</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3">
         <f>F4-G4-H4</f>
@@ -1388,25 +1389,25 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>23039</v>
+        <v>71382</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2987.84</v>
+        <v>8864.929999999995</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2309</v>
+        <v>6686.599999999996</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>3177.793103448275</v>
+        <v>9845.793103448268</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3">
         <f>F5-G5-H5</f>
@@ -1428,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1542,19 +1543,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 Nueva Original Color</t>
+          <t>Parlante Bluetooth Jbl Flip 7 Resistente Al Agua Y Polvo Ip6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>CLARIBEL</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7787</v>
+        <v>29877</v>
       </c>
     </row>
     <row r="6">
@@ -1565,19 +1566,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Parlante Bluetooth Jbl Flip 7 Resistente Al Agua Y Polvo Ip6</t>
+          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 Nueva Original Color</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLARIBEL</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6495</v>
+        <v>11381</v>
       </c>
     </row>
     <row r="7">
@@ -1588,7 +1589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Cel</t>
+          <t>Bocina Jbl Grip Bluetooth Portátil Ip68 14 H Batería Negro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1597,10 +1598,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2874</v>
+        <v>9660</v>
       </c>
     </row>
     <row r="8">
@@ -1620,10 +1621,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2188</v>
+        <v>7505</v>
       </c>
     </row>
     <row r="9">
@@ -1634,7 +1635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Armaf Delight Island Bliss Edp 100 Ml Para Mujer</t>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Cel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1643,10 +1644,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2109</v>
+        <v>6706</v>
       </c>
     </row>
     <row r="10">
@@ -1666,10 +1667,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1809</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="11">
@@ -1680,7 +1681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Angel Nova Fruitté Edp Para Mujer</t>
+          <t>Parlante Bluetooth Jbl Go 4 Portátil Rosa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1689,10 +1690,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1743</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="12">
@@ -1703,7 +1704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Parlante Bluetooth Jbl Go 4 Portátil Rosa</t>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Azu</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1712,10 +1713,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1497</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="13">
@@ -1726,7 +1727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Azu</t>
+          <t>Armaf Delight Island Bliss Edp 100 Ml Para Mujer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1735,10 +1736,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1268</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="14">
@@ -1749,7 +1750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bocina Jbl Grip Bluetooth Portátil Ip68 14 H Batería Negro</t>
+          <t>Angel Nova Fruitté Edp Para Mujer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1761,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>966</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="15">
@@ -1772,7 +1773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Armaf Odyssey Mega Man Edición Limitada Edp 100 Ml</t>
+          <t>Altavoz Bluetooth Azul Impermeable Jbl Go4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1781,10 +1782,10 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>897</v>
+        <v>998</v>
       </c>
     </row>
     <row r="16">
@@ -1795,7 +1796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Armaf Club De Nuit Maleka Edp Mujer 105ml</t>
+          <t>Armaf Odyssey Mega Man Edición Limitada Edp 100 Ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1804,10 +1805,10 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>499</v>
+        <v>897</v>
       </c>
     </row>
     <row r="17">
@@ -1818,7 +1819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Perfume Lattafa His Confession 100ml Edp Para Caballero</t>
+          <t>Sony Srs-xb100 Altavoz De Viaje Inalámbrico Bluetooth Port C</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1830,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>395</v>
+        <v>690</v>
       </c>
     </row>
     <row r="18">
@@ -1841,18 +1842,110 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Perfume Armaf Odyssey Spectra Hombre 100ml Eau De Parfum</t>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Cel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLARIBEL</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Armaf Club De Nuit Maleka Edp Mujer 105ml</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Altavoz Bluetooth Jbl Go 4 Rosa Rosa Chicle</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Perfume Lattafa His Confession 100ml Edp Para Caballero</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Perfume Armaf Odyssey Spectra Hombre 100ml Eau De Parfum</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLARIBEL</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>299</v>
       </c>
     </row>
@@ -1867,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1935,66 +2028,6 @@
         <v>599</v>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>JUAN</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2000016142393670</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 Nueva Original Color</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>599</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CLARIBEL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2000016143278512</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bocina Portátil Jbl Go 4 Bluetooth, Camuflaje. Color Camufla</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>603</v>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>cancelled</t>
         </is>
@@ -2067,31 +2100,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 Nueva Original Color</t>
+          <t>Parlante Bluetooth Jbl Flip 7 Resistente Al Agua Y Polvo Ip6</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7787</v>
+        <v>29877</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Parlante Bluetooth Jbl Flip 7 Resistente Al Agua Y Polvo Ip6</t>
+          <t>Bocina Jbl Go 4 Bluetooth Portatil Ip67 Nueva Original Color</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6495</v>
+        <v>11381</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Cel</t>
+          <t>Bocina Jbl Grip Bluetooth Portátil Ip68 14 H Batería Negro</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2874</v>
+        <v>9660</v>
       </c>
     </row>
     <row r="44">
@@ -2101,17 +2134,17 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2188</v>
+        <v>7505</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Armaf Delight Island Bliss Edp 100 Ml Para Mujer</t>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Cel</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2109</v>
+        <v>6706</v>
       </c>
     </row>
     <row r="46">
@@ -2121,47 +2154,47 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1809</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Angel Nova Fruitté Edp Para Mujer</t>
+          <t>Parlante Bluetooth Jbl Go 4 Portátil Rosa</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1743</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Parlante Bluetooth Jbl Go 4 Portátil Rosa</t>
+          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Azu</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1497</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bocina Jbl Go 4 Jblgo4 Portátil Con Bluetooth Waterproof Azu</t>
+          <t>Armaf Delight Island Bliss Edp 100 Ml Para Mujer</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1268</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bocina Jbl Grip Bluetooth Portátil Ip68 14 H Batería Negro</t>
+          <t>Angel Nova Fruitté Edp Para Mujer</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>966</v>
+        <v>1743</v>
       </c>
     </row>
   </sheetData>
